--- a/results/Int All Data -0.8/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_3_permute.xlsx
@@ -440,1347 +440,1347 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8402822232883631</v>
+        <v>0.8153074425233586</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8363633933483124</v>
+        <v>0.8177593712144767</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8362510147488558</v>
+        <v>0.8185571009909014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8312185990627027</v>
+        <v>0.8198205248696127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8302122917918249</v>
+        <v>0.8198205248696127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8296180393856214</v>
+        <v>0.8070475275301189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8208489913009467</v>
+        <v>0.8132735481529109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8220162162846615</v>
+        <v>0.8149652066007567</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8244681449757796</v>
+        <v>0.8130326112495375</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8199388829250654</v>
+        <v>0.8130326112495375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8204420365605043</v>
+        <v>0.8114158718679961</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8189589556071117</v>
+        <v>0.8140014589872631</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8167105042862148</v>
+        <v>0.8114958910585326</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8134284864097517</v>
+        <v>0.8114958910585326</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8137068828462773</v>
+        <v>0.8134284864097517</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8189265961981915</v>
+        <v>0.8140976578822596</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8172187580458856</v>
+        <v>0.8148042888879197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8208217320162585</v>
+        <v>0.8164746675070733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8206557141791895</v>
+        <v>0.8174222354161068</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8206931737123417</v>
+        <v>0.819354830767326</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8174273355403388</v>
+        <v>0.8185945605240537</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8180965070128468</v>
+        <v>0.8280702396143884</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8204735166376604</v>
+        <v>0.8268817348019815</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.820066561897218</v>
+        <v>0.8214968829447624</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8233536798979131</v>
+        <v>0.8214594234116103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8174920543581793</v>
+        <v>0.824703102423157</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8172885769879581</v>
+        <v>0.8226146894833328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8178291901565492</v>
+        <v>0.8228930859198584</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8194084700049383</v>
+        <v>0.825066618174451</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8182361448969915</v>
+        <v>0.8290229076476539</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.827990220423852</v>
+        <v>0.8263462217576224</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8239802917130368</v>
+        <v>0.8245634645390121</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.822641948768021</v>
+        <v>0.8244885454727076</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8201525605437505</v>
+        <v>0.7974891912539552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8204684165134284</v>
+        <v>0.7975428304915675</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8262074632052416</v>
+        <v>0.8018413558873724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8262823822715462</v>
+        <v>0.8031209594705437</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8111374754314705</v>
+        <v>0.8042720047497984</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8105432230252672</v>
+        <v>0.804550401186324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8201432396270507</v>
+        <v>0.8052783120206762</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.823821132663728</v>
+        <v>0.8115852311657688</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8236176552935068</v>
+        <v>0.8142780967602603</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8231732410199123</v>
+        <v>0.8137213038872091</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8126852752027035</v>
+        <v>0.8121794835719722</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8141683561560962</v>
+        <v>0.8150758265366851</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8141683561560962</v>
+        <v>0.814219357398416</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8129049322773848</v>
+        <v>0.8201516812119864</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8123906990617178</v>
+        <v>0.8191726332257969</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8136915824735813</v>
+        <v>0.8168322038023712</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8056078855658746</v>
+        <v>0.8141555179123399</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8059075618310922</v>
+        <v>0.8143964548157132</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8059075618310922</v>
+        <v>0.8185885810680575</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8070211475771948</v>
+        <v>0.8151141654016014</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7933857016434359</v>
+        <v>0.819884364355689</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7929574670743014</v>
+        <v>0.8197456058033082</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7942421707817049</v>
+        <v>0.8186856592948182</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7957465315637895</v>
+        <v>0.8185732806953614</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7918124012510429</v>
+        <v>0.8198579844027649</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7856238401614031</v>
+        <v>0.8188193177229668</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7895052105683016</v>
+        <v>0.8184983616290571</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7893017331980803</v>
+        <v>0.8159127745097902</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7847835507275942</v>
+        <v>0.8161911709463158</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7884827235929637</v>
+        <v>0.8162660900126202</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7881294080901335</v>
+        <v>0.8162660900126202</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7944890871410744</v>
+        <v>0.8120314041028917</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7942106907045487</v>
+        <v>0.8120314041028917</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7965595617129101</v>
+        <v>0.8162124507750079</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7977106069921649</v>
+        <v>0.8006222503295736</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7979890034286905</v>
+        <v>0.7986470953209701</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8011050034680844</v>
+        <v>0.7906077167341758</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8004732915287288</v>
+        <v>0.787497696150778</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.802047471252886</v>
+        <v>0.7785098703231861</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8020849307860383</v>
+        <v>0.7854425219516381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7996704616280722</v>
+        <v>0.7856459993218594</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7971112544617294</v>
+        <v>0.7853088635234894</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7904714203107348</v>
+        <v>0.7827820157660668</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7922005382917328</v>
+        <v>0.7827820157660668</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7934052228085997</v>
+        <v>0.7837670432082524</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7892241761364835</v>
+        <v>0.7843987551476082</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7897435094763825</v>
+        <v>0.7848269897167426</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7825699209445571</v>
+        <v>0.7332691303901279</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7860868962683973</v>
+        <v>0.7332691303901279</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7864402117712275</v>
+        <v>0.7392712731457707</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7682227438809062</v>
+        <v>0.7364123897142101</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7713872830336805</v>
+        <v>0.7360003348495358</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7629664503276039</v>
+        <v>0.7337084445394905</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7669865792868831</v>
+        <v>0.725024515769584</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7683411019363589</v>
+        <v>0.7229897420673723</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7666869030216653</v>
+        <v>0.716034931278464</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7650276039827397</v>
+        <v>0.7143160135459299</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7679775861850648</v>
+        <v>0.7206969724255627</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7585019070947301</v>
+        <v>0.7121841616169574</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.755712842605242</v>
+        <v>0.7171263578641102</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6841529995061673</v>
+        <v>0.7083778861427164</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6732802381089724</v>
+        <v>0.7052406062746301</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6833033891556586</v>
+        <v>0.7181966804874171</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6645504082209781</v>
+        <v>0.710547197604841</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.684925228661432</v>
+        <v>0.7267640098653989</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6872579199653333</v>
+        <v>0.7368816011435534</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6625956537093027</v>
+        <v>0.719857738189871</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6338051006870044</v>
+        <v>0.7166191593025563</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6241285822217407</v>
+        <v>0.7183644569880143</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6214195369227891</v>
+        <v>0.7168064569683174</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6171261116512162</v>
+        <v>0.7180698808470287</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6423409499878301</v>
+        <v>0.7152859164817725</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.622442023898127</v>
+        <v>0.7007940014097447</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6249688716555496</v>
+        <v>0.6552801410307456</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6118212789845336</v>
+        <v>0.6470568062388941</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5876535489126535</v>
+        <v>0.6317995207993619</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5392546010155227</v>
+        <v>0.59863464398319</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5395117176233561</v>
+        <v>0.5998767880332092</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5250998217418648</v>
+        <v>0.5942773792255408</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5235894815037839</v>
+        <v>0.5673733445700209</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5235894815037839</v>
+        <v>0.5209715349755968</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5235894815037839</v>
+        <v>0.5209715349755968</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5209340754424446</v>
+        <v>0.5193122359366712</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5236593004458564</v>
+        <v>0.5220749204732352</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.506609936871014</v>
+        <v>0.5377493609016738</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5089324279264513</v>
+        <v>0.5444078368860682</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5117496310323918</v>
+        <v>0.5441806175582153</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5084088737940844</v>
+        <v>0.5208396352109763</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5030504018897894</v>
+        <v>0.5166109287572439</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5030504018897894</v>
+        <v>0.5176981345504222</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4998918421930112</v>
+        <v>0.5188066201722927</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5006895719694359</v>
+        <v>0.5151074473069234</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4959415321758044</v>
+        <v>0.5173184390946681</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4957755143387355</v>
+        <v>0.5180250701003283</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4977242893944148</v>
+        <v>0.5120076269719894</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4972960548252803</v>
+        <v>0.5103159685241436</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4972960548252803</v>
+        <v>0.5104819863612126</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5004869739309789</v>
+        <v>0.5104819863612126</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5001498381326088</v>
+        <v>0.5085493910099934</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5005406131685911</v>
+        <v>0.5081424362695511</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.498275982143234</v>
+        <v>0.5179552511582558</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.498275982143234</v>
+        <v>0.5182711071279337</v>
       </c>
     </row>
     <row r="137">
@@ -1790,193 +1790,193 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4985543785797596</v>
+        <v>0.5161350344064933</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.5134047092788494</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4997216035634744</v>
+        <v>0.5065418765924699</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5037630123514457</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5044645432328737</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5021786323788245</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5047267599649393</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5047267599649393</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.503126200287858</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5039664897216669</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5055295898655959</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5054546707992915</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5054546707992915</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4992661097096517</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4978741275270236</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4978741275270236</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4972585952921281</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4978153881651793</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4978903072314838</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B156" t="n">
